--- a/jira_export_2026-08-07.xlsx
+++ b/jira_export_2026-08-07.xlsx
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -8615,7 +8615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8639,7 +8639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 4 commande(s)</t>
+          <t>Épics créées ce mois — 5 commande(s)</t>
         </is>
       </c>
     </row>
@@ -8739,22 +8739,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -8774,22 +8774,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34970</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34966</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -8819,83 +8819,107 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00146508</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I9" s="25" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>4 commande(s)</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="n">
-        <v>8550</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" s="17" t="n"/>
@@ -8906,17 +8930,17 @@
       <c r="G10" s="17" t="n"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>3 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>4500</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B11" s="17" t="n"/>
@@ -8927,10 +8951,31 @@
       <c r="G11" s="17" t="n"/>
       <c r="H11" s="17" t="inlineStr">
         <is>
+          <t>4 commande(s)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
           <t>1 commande(s)</t>
         </is>
       </c>
-      <c r="I11" s="24" t="n">
+      <c r="I12" s="24" t="n">
         <v>4050</v>
       </c>
     </row>

--- a/jira_export_2026-08-07.xlsx
+++ b/jira_export_2026-08-07.xlsx
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>387238</v>
+        <v>388738</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>145143</v>
+        <v>146643</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>242094</v>
@@ -8561,10 +8561,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>173204</v>
+        <v>174704</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69479</v>
+        <v>70979</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103725</v>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>8550</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="11">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="12">

--- a/jira_export_2026-08-07.xlsx
+++ b/jira_export_2026-08-07.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>86 h</t>
+          <t>92 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6535,7 +6535,7 @@
         <v>13</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>13</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>13</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>13</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>35</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -7716,7 +7716,7 @@
         <v>367.5</v>
       </c>
       <c r="P99" s="18" t="n">
-        <v>7.74</v>
+        <v>7.46</v>
       </c>
     </row>
   </sheetData>
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>37.25</v>
+        <v>38.5</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>47.5</v>
+        <v>49.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>8</v>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>30.75</v>
+        <v>34.25</v>
       </c>
     </row>
   </sheetData>
